--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_touch_size.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_touch_size.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C2" t="n">
-        <v>55.5</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>
